--- a/assets/data/template_input_qda.xlsx
+++ b/assets/data/template_input_qda.xlsx
@@ -1,63 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awp/Documents/R-Studio/Praktikum Uji Sensoris/praktikum-uji-sensoris-TPHP/assets/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E03798-C2DB-B94F-B3B1-B925CCBB1C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk Pengisian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Petunjuk Pengisian" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <si>
+    <t>panelis</t>
+  </si>
+  <si>
+    <t>produk</t>
+  </si>
+  <si>
+    <t>replikasi</t>
+  </si>
+  <si>
+    <t>kerenyahan</t>
+  </si>
+  <si>
+    <t>kekerasan</t>
+  </si>
+  <si>
+    <t>kejuisian</t>
+  </si>
+  <si>
+    <t>kekenyalan</t>
+  </si>
+  <si>
+    <t>gurih</t>
+  </si>
+  <si>
+    <t>asin</t>
+  </si>
+  <si>
+    <t>aroma_ayam</t>
+  </si>
+  <si>
+    <t>aroma_rempah</t>
+  </si>
+  <si>
+    <t>P01</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Template input data QDA - HAPUS baris kuning sebelum menginput data asli</t>
+  </si>
+  <si>
+    <t>Kolom</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Baris kuning</t>
+  </si>
+  <si>
+    <t>Baris contoh berisi format nilai yang diharapkan. Hapus sebelum menginput data asli.</t>
+  </si>
+  <si>
+    <t>Satu baris</t>
+  </si>
+  <si>
+    <t>Satu panelis menilai satu produk pada satu replikasi. Jangan membuat satu baris per panelis.</t>
+  </si>
+  <si>
+    <t>Kode panelis, format teks konsisten (P01, P02, ...). Jangan campur P1 dan P01.</t>
+  </si>
+  <si>
+    <t>Kode produk berupa huruf atau kode 3 digit. Tulis sama persis di semua baris.</t>
+  </si>
+  <si>
+    <t>Angka ulangan: 1, 2, dst.</t>
+  </si>
+  <si>
+    <t>Kolom atribut</t>
+  </si>
+  <si>
+    <t>Satu kolom untuk satu atribut. Nama kolom tanpa spasi (pakai garis bawah), tanpa tanda baca, dan tidak diawali angka.</t>
+  </si>
+  <si>
+    <t>Nilai atribut</t>
+  </si>
+  <si>
+    <t>Angka saja. Gunakan titik sebagai pemisah desimal (10.9), bukan koma.</t>
+  </si>
+  <si>
+    <t>Sel kosong</t>
+  </si>
+  <si>
+    <t>Biarkan benar-benar kosong jika data hilang. Jangan diisi tanda hubung, 'NA' manual, atau angka 0.</t>
+  </si>
+  <si>
+    <t>Menambah atribut</t>
+  </si>
+  <si>
+    <t>Boleh menambah kolom atribut baru di sebelah kanan, dan menambah baris ke bawah sesuai jumlah panelis.</t>
+  </si>
+  <si>
+    <t>Menyimpan</t>
+  </si>
+  <si>
+    <t>Simpan sebagai .xlsx di folder assets/data/ pada proyek RStudio Anda.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Arial"/>
-      <b val="1"/>
+      <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
       <name val="Arial"/>
-      <i val="1"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,91 +188,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -445,122 +502,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col min="1" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>panelis</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>produk</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>replikasi</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>kerenyahan</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>kekerasan</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>kejuisian</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>kekenyalan</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>gurih</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>asin</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>aroma_ayam</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>aroma_rempah</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>P01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>10.9</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>7.1</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>8.9</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>7.5</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>12.7</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2">
         <v>8.5</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="J2" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K2" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H14" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -568,155 +595,105 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Template input data QDA - HAPUS baris kuning sebelum menginput data asli</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Kolom</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Keterangan</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Baris kuning</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Baris contoh berisi format nilai yang diharapkan. Hapus sebelum menginput data asli.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Satu baris</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Satu panelis menilai satu produk pada satu replikasi. Jangan membuat satu baris per panelis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>panelis</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Kode panelis, format teks konsisten (P01, P02, ...). Jangan campur P1 dan P01.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>produk</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Kode produk berupa huruf atau kode 3 digit. Tulis sama persis di semua baris.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>replikasi</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Angka ulangan: 1, 2, dst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Kolom atribut</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Satu kolom untuk satu atribut. Nama kolom tanpa spasi (pakai garis bawah), tanpa tanda baca, dan tidak diawali angka.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Nilai atribut</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Angka saja. Gunakan titik sebagai pemisah desimal (10.9), bukan koma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Sel kosong</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Biarkan benar-benar kosong jika data hilang. Jangan diisi tanda hubung, 'NA' manual, atau angka 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Menambah atribut</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Boleh menambah kolom atribut baru di sebelah kanan, dan menambah baris ke bawah sesuai jumlah panelis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Menyimpan</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Simpan sebagai .xlsx di folder assets/data/ pada proyek RStudio Anda.</t>
-        </is>
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
